--- a/reports/jobs_2026-10-31.xlsx
+++ b/reports/jobs_2026-10-31.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Western Digital India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Verification Engineer</t>
+          <t>Engineer, Data Analytics Engineering</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -538,7 +538,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -546,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/chandler/verification-engineer/33099/102632900560</t>
+          <t>https://api.smartrecruiters.com/v1/companies/WesternDigital/postings/744000158892829</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careers.smartrecruiters.com/WesternDigital</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -563,12 +567,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Agnikul Cosmos</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -581,11 +585,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 1 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -593,12 +593,12 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>mailto:%20humancapital@agnikul.in</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://agnikul.in/careers</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Chiang Mai 1 available jobs</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 1 available jobs</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 2 available jobs</t>
+          <t>Mumbai 1 available jobs</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Shanghai 2 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -769,7 +769,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 1 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -777,7 +781,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -799,7 +803,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Key Takeaways from Tech at Agoda: From Assistants to AI Agents October 27, 2026 /</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -820,7 +824,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-tech-at-agoda-from-assistants-to-ai-agents/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -842,7 +846,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>How We Cut the Coupling Tax in a Post-Booking API October 20, 2026 /</t>
+          <t>Key Takeaways from Tech at Agoda: From Assistants to AI Agents October 27, 2026 /</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -863,7 +867,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/blog/tech/how-we-cut-the-coupling-tax-in-a-post-booking-api/</t>
+          <t>https://careersatagoda.com/blog/tech/key-takeaways-from-tech-at-agoda-from-assistants-to-ai-agents/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -885,7 +889,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>How We Cut the Coupling Tax in a Post-Booking API October 20, 2026 /</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -898,11 +902,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -910,7 +910,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/blog/tech/how-we-cut-the-coupling-tax-in-a-post-booking-api/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -945,7 +945,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai jobs Yokohama jobs</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -953,7 +957,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -975,12 +979,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -996,7 +1000,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1018,12 +1022,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1039,7 +1043,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1056,17 +1060,17 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Compiler Engineer (Machine Learning)</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1082,12 +1086,12 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1099,17 +1103,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Verification Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1125,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27443</t>
+          <t>https://careers.arm.com/job/chandler/verification-engineer/33099/102632900560</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1142,17 +1146,17 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Application Development Engineer</t>
+          <t>Compiler Engineer (Machine Learning)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1160,11 +1164,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E16" s="4" t="inlineStr"/>
       <c r="F16" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26833</t>
+          <t>https://careers.arm.com/job/lund/compiler-engineer-machine-learning/33099/94847322016</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1207,11 +1207,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru or Remote</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -1219,7 +1215,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27589</t>
+          <t>https://www.atlassian.com/company/careers/details/27443</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1241,12 +1237,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Application Development Engineer</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1266,7 +1262,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27794</t>
+          <t>https://www.atlassian.com/company/careers/details/26833</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1288,12 +1284,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1303,7 +1299,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bengaluru or Remote</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1313,7 +1309,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25538</t>
+          <t>https://www.atlassian.com/company/careers/details/27589</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1335,7 +1331,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer - Focus Funds and AI</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1360,7 +1356,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27824</t>
+          <t>https://www.atlassian.com/company/careers/details/27794</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1407,7 +1403,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27823</t>
+          <t>https://www.atlassian.com/company/careers/details/25538</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1429,7 +1425,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer - Identity</t>
+          <t>Backend Software Engineer - Focus Funds and AI</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1454,7 +1450,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27819</t>
+          <t>https://www.atlassian.com/company/careers/details/27824</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1476,12 +1472,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1501,7 +1497,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26674</t>
+          <t>https://www.atlassian.com/company/careers/details/27823</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1523,12 +1519,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Backend Software Engineer - Identity</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25561</t>
+          <t>https://www.atlassian.com/company/careers/details/27819</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1570,12 +1566,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1595,7 +1591,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/24899</t>
+          <t>https://www.atlassian.com/company/careers/details/26674</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1617,12 +1613,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>AI Researcher, 2027 Graduate U.S.</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1642,7 +1638,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26246</t>
+          <t>https://www.atlassian.com/company/careers/details/25561</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1664,12 +1660,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>EMEA Field CTO, DX — Engineering Executive Advisor</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1689,7 +1685,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25539</t>
+          <t>https://www.atlassian.com/company/careers/details/24899</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1711,7 +1707,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Engineer</t>
+          <t>AI Researcher, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1736,7 +1732,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27455</t>
+          <t>https://www.atlassian.com/company/careers/details/26246</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1758,12 +1754,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Principle Machine Learning Systems Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27796</t>
+          <t>https://www.atlassian.com/company/careers/details/25539</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1805,12 +1801,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Principle Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1818,7 +1814,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26758</t>
+          <t>https://www.atlassian.com/company/careers/details/27455</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Principle Machine Learning Systems Engineer</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25566</t>
+          <t>https://www.atlassian.com/company/careers/details/27796</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1908,11 +1908,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E32" s="4" t="inlineStr"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -1920,7 +1916,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27431</t>
+          <t>https://www.atlassian.com/company/careers/details/26758</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1942,12 +1938,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>AI Researcher (PhD), 2027 Graduate Canada</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1967,7 +1963,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26074</t>
+          <t>https://www.atlassian.com/company/careers/details/25566</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1989,12 +1985,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer, 2027 Graduate U.S.</t>
+          <t>Software Engineer – Full Stack (Loom Billing &amp; Integrations)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2002,7 +1998,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr"/>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25997</t>
+          <t>https://www.atlassian.com/company/careers/details/27431</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate Canada</t>
+          <t>AI Researcher (PhD), 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2045,7 +2045,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2053,7 +2057,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26070</t>
+          <t>https://www.atlassian.com/company/careers/details/26074</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2075,12 +2079,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
+          <t>Security Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2096,7 +2100,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25999</t>
+          <t>https://www.atlassian.com/company/careers/details/25997</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2118,12 +2122,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer, 2027 Graduate U.S</t>
+          <t>Software Engineer, 2027 Graduate Canada</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25998</t>
+          <t>https://www.atlassian.com/company/careers/details/26070</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2161,12 +2165,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, 2027 Graduate U.S.</t>
+          <t>Machine Learning Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -2182,7 +2186,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/25813</t>
+          <t>https://www.atlassian.com/company/careers/details/25999</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2204,12 +2208,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>AI Research Intern (PhD), 2027 Summer U.S.</t>
+          <t>Data Engineer, 2027 Graduate U.S</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2217,11 +2221,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26269</t>
+          <t>https://www.atlassian.com/company/careers/details/25998</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Canada</t>
+          <t>Software Engineer, 2027 Graduate U.S.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26275</t>
+          <t>https://www.atlassian.com/company/careers/details/25813</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Data Engineer Intern, 2027 Summer U.S.</t>
+          <t>AI Research Intern (PhD), 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26272</t>
+          <t>https://www.atlassian.com/company/careers/details/26269</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Research Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Canada</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26270</t>
+          <t>https://www.atlassian.com/company/careers/details/26275</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Intern, 2027 Summer U.S.</t>
+          <t>Data Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2397,7 +2397,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2405,7 +2409,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26268</t>
+          <t>https://www.atlassian.com/company/careers/details/26272</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2427,7 +2431,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Security Engineer Intern, 2027 Summer U.S.</t>
+          <t>Research Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -2448,7 +2452,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26267</t>
+          <t>https://www.atlassian.com/company/careers/details/26270</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2470,12 +2474,12 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Intern, 2027 Summer U.S.</t>
+          <t>Machine Learning Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2491,7 +2495,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26266</t>
+          <t>https://www.atlassian.com/company/careers/details/26268</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -2513,7 +2517,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Product Design Intern, 2027 Summer U.S.</t>
+          <t>Security Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2526,11 +2530,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr"/>
       <c r="F46" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26273</t>
+          <t>https://www.atlassian.com/company/careers/details/26267</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Product Management Intern, 2027 Summer U.S.</t>
+          <t>Software Engineer Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2573,11 +2573,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr"/>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2585,7 +2581,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26274</t>
+          <t>https://www.atlassian.com/company/careers/details/26266</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2607,7 +2603,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
+          <t>Product Design Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2632,7 +2628,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26843</t>
+          <t>https://www.atlassian.com/company/careers/details/26273</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -2654,12 +2650,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Enterprise Security Engineer</t>
+          <t>Product Management Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2679,7 +2675,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/27275</t>
+          <t>https://www.atlassian.com/company/careers/details/26274</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2701,12 +2697,12 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Security Testing Engineer - Penetration Tester</t>
+          <t>AI Demand Intelligence Intern, 2027 Summer U.S.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2716,7 +2712,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Remote or Remote</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2726,7 +2722,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/details/26643</t>
+          <t>https://www.atlassian.com/company/careers/details/26843</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -2743,12 +2739,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>Enterprise Security Engineer</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2761,7 +2757,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2769,12 +2769,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/details/27275</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2786,17 +2786,17 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Security Testing Engineer - Penetration Tester</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2804,7 +2804,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Remote or Remote</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2812,12 +2816,12 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.atlassian.com/company/careers/details/26643</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -2829,17 +2833,17 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Commvault India</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Python)</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2847,11 +2851,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, India; Hyderbad, India; Pune, India</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/commvault/jobs/5440365008</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/commvault</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
@@ -2876,17 +2876,17 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2894,11 +2894,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>India Full-time</t>
-        </is>
-      </c>
+      <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -2906,12 +2902,12 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -2923,17 +2919,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Commvault India</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 3</t>
+          <t>Software Engineer (Python)</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2943,7 +2939,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore, India; Hyderbad, India; Pune, India</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2953,12 +2949,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer-3</t>
+          <t>https://job-boards.greenhouse.io/commvault/jobs/5440365008</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://boards.greenhouse.io/commvault</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2975,12 +2971,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer - 1</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -3000,7 +2996,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3022,7 +3018,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2</t>
+          <t>Integration &amp; Customisation Engineer - 3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -3035,7 +3031,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr"/>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer-3</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Integration &amp; Customization Engineer - 1</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-710627-implementation-engineer</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Billing)</t>
+          <t>Integration and Customisation Engineer - 2</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -3125,11 +3125,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E59" s="4" t="inlineStr"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3137,7 +3133,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3159,7 +3155,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3184,7 +3180,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-710627-implementation-engineer</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3206,7 +3202,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Software Engineer - 2 (Billing)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3231,7 +3227,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-700106-software-engineer-2-billing</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3253,7 +3249,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3278,7 +3274,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3300,7 +3296,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3325,7 +3321,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice4AI)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -3372,7 +3368,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice4ai</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3394,12 +3390,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3419,7 +3415,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3441,7 +3437,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer-2 (AIX)</t>
+          <t>Software Engineer - 3 (Voice4AI)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -3466,7 +3462,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-711044-software-engineer2-aix</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice4ai</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3483,17 +3479,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Facilio</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Mobile CMMS Every job on the phone, offline</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3501,7 +3497,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://facilio.com/product/mobile-cmms-app/</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://facilio.com/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3526,12 +3526,12 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CA Industrial Trainee</t>
+          <t>Software Engineer-2 (AIX)</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3544,7 +3544,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3552,12 +3556,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Mumbai/CA-Industrial-Trainee_SR-46509-1</t>
+          <t>https://exotel.com/about-us/careers/#op-711044-software-engineer2-aix</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3569,17 +3573,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Facilio</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer- WD</t>
+          <t>Mobile CMMS Every job on the phone, offline</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3595,12 +3599,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
+          <t>https://facilio.com/product/mobile-cmms-app/</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://facilio.com/careers/</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3617,12 +3621,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Gen AI Engineer-AWS</t>
+          <t>CA Industrial Trainee</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3638,7 +3642,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
+          <t>https://fractal.ai/en-US/Careers/job/Mumbai/CA-Industrial-Trainee_SR-46509-1</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3660,12 +3664,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
+          <t>Full Stack Developer- WD</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3681,7 +3685,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Full-Stack-Developer--WD_SR-45696-1</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3698,17 +3702,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Gen AI Engineer-AWS</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3724,12 +3728,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/Bengaluru/Gen-AI-Engineer-AWS_SR-47131</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3741,17 +3745,17 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>CPGR Growth Leader, AI Engineering, Strategic Accounts</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3767,12 +3771,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/CPGR-Growth-Leader--AI-Engineering--Strategic-Accounts_SR-46966</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -3784,12 +3788,12 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3810,12 +3814,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3827,17 +3831,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3845,11 +3849,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad, Telangana, India</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3874,17 +3874,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3892,11 +3892,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E76" s="4" t="inlineStr"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3904,12 +3900,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3921,17 +3917,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3939,7 +3935,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Hyderabad, Telangana, India</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3947,12 +3947,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -3964,17 +3964,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3982,7 +3982,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr"/>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -3990,12 +3994,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4007,17 +4011,17 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -4033,12 +4037,12 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -4050,12 +4054,12 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4068,11 +4072,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I80" s="4" t="inlineStr">
@@ -4097,17 +4097,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4140,12 +4140,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Open Financial</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -4158,7 +4158,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr"/>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4166,12 +4170,12 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://open.money/company/careers</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>https://open.money/careers</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I82" s="4" t="inlineStr">
@@ -4183,17 +4187,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4209,12 +4213,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4226,17 +4230,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Open Financial</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Intern - Talent Acquisition</t>
+          <t>We’re hiring Build with us Roles across engineering, product and GTM.</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4244,11 +4248,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, Haryana</t>
-        </is>
-      </c>
+      <c r="E84" s="4" t="inlineStr"/>
       <c r="F84" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
+          <t>https://open.money/company/careers</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://open.money/careers</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4273,12 +4273,12 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4291,11 +4291,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4303,12 +4299,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4325,7 +4321,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Intern - Talent Acquisition</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4340,7 +4336,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -4350,7 +4346,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/426a6834-1397-4e65-94af-69874c790805</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4372,7 +4368,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4387,7 +4383,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -4397,7 +4393,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -4419,7 +4415,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4434,7 +4430,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -4444,7 +4440,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -4466,7 +4462,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - IT Recruitment</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4491,7 +4487,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
+          <t>https://jobs.lever.co/paytm/6d7551f7-34c3-46a2-a4e4-18b29f15338c</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4508,17 +4504,17 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -4526,7 +4522,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr"/>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I90" s="4" t="inlineStr">
@@ -4551,17 +4551,17 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Talent Acquisition Intern - IT Recruitment</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Indore, in</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://jobs.lever.co/paytm/95eadc2b-27bf-40fe-b6e6-93aaeadd08f7</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -4598,12 +4598,12 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4616,11 +4616,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E92" s="4" t="inlineStr"/>
       <c r="F92" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4628,12 +4624,12 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I92" s="4" t="inlineStr">
@@ -4650,7 +4646,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -4675,7 +4671,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -4692,17 +4688,17 @@
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -4710,7 +4706,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr"/>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I94" s="4" t="inlineStr">
@@ -4735,17 +4735,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>AI Builder</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Indore, in</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4744950005</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
@@ -4782,12 +4782,12 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -4800,11 +4800,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E96" s="4" t="inlineStr"/>
       <c r="F96" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -4812,12 +4808,12 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I96" s="4" t="inlineStr">
@@ -4829,12 +4825,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Industrial Trainee</t>
+          <t>AI Builder</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4849,7 +4845,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -4859,12 +4855,12 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4744950005</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
@@ -4881,12 +4877,12 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -4906,7 +4902,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8305308?gh_jid=8305308</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -4928,7 +4924,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>Industrial Trainee</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -4943,7 +4939,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -4953,7 +4949,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8266405?gh_jid=8266405</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -4975,7 +4971,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud: Azure</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -4985,12 +4981,12 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>0-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bangalore </t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -5000,7 +4996,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8305308?gh_jid=8305308</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5022,7 +5018,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5037,7 +5033,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -5047,7 +5043,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -5069,7 +5065,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer- SaaS O365</t>
+          <t>Software Engineer - Cloud: Azure</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5094,7 +5090,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8258200?gh_jid=8258200</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -5111,12 +5107,12 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5129,7 +5125,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5137,12 +5137,12 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
@@ -5154,12 +5154,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>Software Engineer- SaaS O365</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -5169,10 +5169,14 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr"/>
+          <t>0-2 years</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bangalore </t>
+        </is>
+      </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5180,12 +5184,12 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8256407?gh_jid=8256407</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I104" s="4" t="inlineStr">
@@ -5202,7 +5206,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -5223,7 +5227,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -5245,7 +5249,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -5266,7 +5270,7 @@
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -5283,17 +5287,17 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -5301,11 +5305,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E107" s="4" t="inlineStr"/>
       <c r="F107" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
@@ -5330,17 +5330,17 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -5348,11 +5348,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E108" s="4" t="inlineStr"/>
       <c r="F108" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5360,12 +5356,12 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr">
@@ -5377,17 +5373,17 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Intern- Professional Services</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -5395,7 +5391,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr"/>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-professional-services/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
@@ -5420,17 +5420,17 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Intern- Employee Engagement</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -5438,7 +5438,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr"/>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5446,12 +5450,12 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr">
@@ -5463,12 +5467,12 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Intern- Professional Services</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -5489,12 +5493,12 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://www.sirion.ai/jobs/intern-professional-services/</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
@@ -5506,12 +5510,12 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Intern- Employee Engagement</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -5524,11 +5528,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E112" s="4" t="inlineStr"/>
       <c r="F112" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5536,12 +5536,12 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://www.sirion.ai/jobs/intern-employee-engagement/</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr">
@@ -5553,29 +5553,25 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, New Grad</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>new grad</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr"/>
       <c r="F113" s="4" t="inlineStr">
         <is>
           <t>2026-10-31</t>
@@ -5583,12 +5579,12 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8130876</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
@@ -5600,17 +5596,17 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -5620,7 +5616,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -5630,12 +5626,12 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr">
@@ -5647,27 +5643,27 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Software Engineer, New Grad</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>new grad</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -5677,12 +5673,12 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8130876</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
@@ -5694,52 +5690,146 @@
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
           <t>Zscaler India</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Escalation Engineer</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
         <is>
           <t>Bangalore, IND</t>
         </is>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/zscaler/jobs/5263563007</t>
         </is>
       </c>
-      <c r="H116" s="4" t="inlineStr">
+      <c r="H118" s="4" t="inlineStr">
         <is>
           <t>https://boards.greenhouse.io/zscaler</t>
         </is>
       </c>
-      <c r="I116" s="4" t="inlineStr">
+      <c r="I118" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I116"/>
+  <autoFilter ref="A1:I118"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -5856,6 +5946,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId117"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5867,7 +5959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5895,15 +5987,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>INDmoney</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.indmoney.com/careers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Cuemath</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://www.cuemath.com/careers/</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5912,26 +6024,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INDmoney</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.indmoney.com/careers</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -5955,35 +6047,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Signzy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://agnikul.in/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Signzy</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.signzy.com/careers/</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -5992,38 +6064,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ather Energy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.atherenergy.com/careers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6032,18 +6084,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6052,18 +6104,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6072,18 +6124,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Cleartrip</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.cleartrip.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6092,18 +6144,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -6112,18 +6164,38 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gupshup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.gupshup.io/careers</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.gupshup.io/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6132,18 +6204,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -6152,38 +6224,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OYO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.oyorooms.com/careers/</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -6192,6 +6244,46 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tata 1mg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.1mg.com/jobs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.1mg.com/jobs", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -6292,26 +6384,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Birlasoft</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://www.birlasoft.com/careers</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.birlasoft.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
